--- a/02_DIA_inicio_2026_analisis_assets/rbd_9716_escuela-basica-acapulco_nt2_rubricas.xlsx
+++ b/02_DIA_inicio_2026_analisis_assets/rbd_9716_escuela-basica-acapulco_nt2_rubricas.xlsx
@@ -1992,13 +1992,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D18CCF0A-95F9-4709-8EA0-7E7EBCA5E191}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2EA3AFD2-76FC-46F2-83A7-24822577F788}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B7F0076D-C96D-4031-A3D7-21F492E4C47F}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{923D9348-346C-4449-9118-9D4E81A33AE8}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3B177157-184B-4B21-9942-AF07D778BE45}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D808961E-1205-4BD2-8C70-6ECA5D5C2D72}"/>
 </file>